--- a/Notes on Experiments.xlsx
+++ b/Notes on Experiments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Mini Imagenet Classification\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niraj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5531EF7B-83E2-43D6-931D-E4C543037DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9A2EDD-C9CB-4297-BE91-55702A83BE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{C5C572F4-9094-4D08-B9FE-0533E188A5DE}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C5C572F4-9094-4D08-B9FE-0533E188A5DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -182,13 +182,6 @@
 After 100 epochs, training accuracy is 57.2% and validation accuracy is 53.9%.</t>
   </si>
   <si>
-    <t>Model architecture:
-Conv (64) -&gt; Conv (96) -&gt; Conv (128) -&gt; Conv (128)
-FC (512) -&gt; FC (256)
-This model has close to n.n million parameters.
-After 100 epochs, training accuracy is 61.9% and validation accuracy is 54.9%.</t>
-  </si>
-  <si>
     <t>The model has trained well, considering that the 50 image classes are at different levels (some are individual breeds of dogs and others are more straightforward, such as iPod or school bus).
 The model is overfitting slightly. Try training with an additional FC layer.</t>
   </si>
@@ -229,6 +222,13 @@
   </si>
   <si>
     <t>ResNet18_</t>
+  </si>
+  <si>
+    <t>Model architecture:
+Conv (64) -&gt; Conv (96) -&gt; Conv (128) -&gt; Conv (128)
+FC (512) -&gt; FC (256)
+This model has close to 13.3 million parameters.
+After 100 epochs, training accuracy is 61.9% and validation accuracy is 54.9%.</t>
   </si>
 </sst>
 </file>
@@ -659,13 +659,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDAF2D2B-9C0C-4AF0-A52C-7D1427445C54}">
   <dimension ref="B1:D17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="4" width="35.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="4" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -676,7 +676,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
@@ -687,7 +687,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
@@ -698,7 +698,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
@@ -709,7 +709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="105" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
         <v>11</v>
       </c>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="135" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="129.6" x14ac:dyDescent="0.3">
       <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
@@ -731,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="150" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" ht="144" x14ac:dyDescent="0.3">
       <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
@@ -742,7 +742,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
@@ -753,7 +753,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
@@ -764,7 +764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
@@ -775,7 +775,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="180" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" ht="144" x14ac:dyDescent="0.3">
       <c r="B11" s="3" t="s">
         <v>30</v>
       </c>
@@ -786,7 +786,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="120" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3" t="s">
         <v>33</v>
       </c>
@@ -797,18 +797,18 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="165" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" ht="144" x14ac:dyDescent="0.3">
       <c r="B13" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" ht="90" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="2:4" ht="72" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>36</v>
       </c>
@@ -816,40 +816,40 @@
         <v>38</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" ht="150" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" ht="144" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="3" t="s">
+    </row>
+    <row r="16" spans="2:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D16" s="3" t="s">
+    <row r="17" spans="2:4" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" ht="165" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
